--- a/genealogy_data.xlsx
+++ b/genealogy_data.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,11 +441,6 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>辈份字</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>描述</t>
         </is>
       </c>
@@ -463,7 +458,6 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,7 +486,6 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -508,7 +500,6 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -523,7 +514,6 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -538,7 +528,6 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -553,7 +542,6 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -568,7 +556,6 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -583,7 +570,6 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -598,7 +584,6 @@
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -613,7 +598,6 @@
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -628,7 +612,6 @@
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -643,7 +626,6 @@
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -658,7 +640,6 @@
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -673,7 +654,6 @@
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -688,7 +668,6 @@
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -703,7 +682,6 @@
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -718,7 +696,6 @@
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -733,7 +710,6 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -748,7 +724,6 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -763,7 +738,6 @@
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -778,7 +752,6 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -793,7 +766,6 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -808,7 +780,6 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -823,7 +794,6 @@
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -838,7 +808,6 @@
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -853,7 +822,6 @@
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -868,7 +836,6 @@
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -883,7 +850,6 @@
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -898,7 +864,6 @@
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -913,7 +878,6 @@
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -928,7 +892,6 @@
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -942,12 +905,7 @@
           <t>第17世</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>粤</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -962,7 +920,6 @@
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -976,12 +933,7 @@
           <t>第18世</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>彩</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -996,7 +948,6 @@
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1010,12 +961,7 @@
           <t>第19世</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>昔</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1030,7 +976,6 @@
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1044,12 +989,7 @@
           <t>第20世</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>粦</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1064,7 +1004,6 @@
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1078,12 +1017,7 @@
           <t>第21世</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>华</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1098,7 +1032,6 @@
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1142,7 +1075,11 @@
           <t>法海公支系</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>法海公</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>法海公后裔</t>
@@ -1255,7 +1192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y107"/>
+  <dimension ref="A1:Z107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1281,105 +1218,110 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>辈份字</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>性别</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>是否为外族配偶</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>世代数</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>世代名称</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>父亲姓名</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>母亲姓名</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>所属支系</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>出生年份</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>逝世年份</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>出生地</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>葬地</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>墓形/风水</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>坐向</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>生平简介</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>主要事迹</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>后裔分布</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>排序</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>账号状态</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>更新时间</t>
         </is>
@@ -1402,60 +1344,61 @@
           <t>法教公、三十七郎</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>第1世</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>葬于凤坑，土名乌坑里张屋后乌鸦落洋形</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>辛山乙向</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>祖于元朝徙居住嘉应州水南坝，后住凤坑，殁于凤坑</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
         <v>1</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X2" s="1" t="n">
-        <v>46055.01161484014</v>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>46055.01161484297</v>
+        <v>46055.0192508086</v>
+      </c>
+      <c r="Z2" s="1" t="n">
+        <v>46055.01925229505</v>
       </c>
     </row>
     <row r="3">
@@ -1467,52 +1410,53 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>第1世（配）</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>葬于平远小柘天弓岌（眼镜形）</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
         <v>2</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X3" s="1" t="n">
-        <v>46055.01161485883</v>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>46055.01161485898</v>
+        <v>46055.01925083798</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>46055.01925230946</v>
       </c>
     </row>
     <row r="4">
@@ -1528,33 +1472,33 @@
           <t>伯一郎</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>第2世</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>乾正公</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>陈氏四娘</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -1565,19 +1509,20 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
         <v>3</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X4" s="1" t="n">
-        <v>46055.01161487523</v>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y4" s="1" t="n">
-        <v>46055.01161487542</v>
+        <v>46055.01925085919</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>46055.01925231932</v>
       </c>
     </row>
     <row r="5">
@@ -1593,33 +1538,33 @@
           <t>伯二郎</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>第2世</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>乾正公</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>陈氏四娘</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1630,19 +1575,20 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
         <v>4</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X5" s="1" t="n">
-        <v>46055.01161489035</v>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>46055.01161489048</v>
+        <v>46055.01925087517</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>46055.01925232942</v>
       </c>
     </row>
     <row r="6">
@@ -1658,33 +1604,33 @@
           <t>伯三郎</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>第2世</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>乾正公</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>陈氏四娘</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1695,19 +1641,20 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
         <v>5</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X6" s="1" t="n">
-        <v>46055.01161490176</v>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>46055.01161490184</v>
+        <v>46055.01925089634</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>46055.01925234022</v>
       </c>
     </row>
     <row r="7">
@@ -1723,33 +1670,33 @@
           <t>伯四郎、万四郎、法远</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>第2世</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>乾正公</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>陈氏四娘</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1760,19 +1707,20 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
         <v>6</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X7" s="1" t="n">
-        <v>46055.01161491818</v>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>46055.01161491836</v>
+        <v>46055.01925090936</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>46055.01925234724</v>
       </c>
     </row>
     <row r="8">
@@ -1788,33 +1736,33 @@
           <t>伯五郎</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>第2世</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>乾正公</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>陈氏四娘</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1825,19 +1773,20 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
         <v>7</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X8" s="1" t="n">
-        <v>46055.01161493273</v>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>46055.01161493287</v>
+        <v>46055.01925092428</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <v>46055.01925235392</v>
       </c>
     </row>
     <row r="9">
@@ -1853,33 +1802,33 @@
           <t>伯六郎</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>第2世</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>乾正公</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>陈氏四娘</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1890,19 +1839,20 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
         <v>8</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X9" s="1" t="n">
-        <v>46055.01161494401</v>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>46055.01161494407</v>
+        <v>46055.01925093857</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <v>46055.01925236075</v>
       </c>
     </row>
     <row r="10">
@@ -1914,23 +1864,23 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>第2世（配）</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1943,19 +1893,20 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
         <v>9</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X10" s="1" t="n">
-        <v>46055.01161495479</v>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>46055.01161495486</v>
+        <v>46055.01925095893</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>46055.01925236729</v>
       </c>
     </row>
     <row r="11">
@@ -1967,23 +1918,23 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>第2世（配）</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1996,19 +1947,20 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
         <v>10</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X11" s="1" t="n">
-        <v>46055.01161496513</v>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>46055.01161496519</v>
+        <v>46055.01925097429</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>46055.01925237361</v>
       </c>
     </row>
     <row r="12">
@@ -2020,23 +1972,23 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>第2世（配）</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -2049,19 +2001,20 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
         <v>11</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X12" s="1" t="n">
-        <v>46055.01161497716</v>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>46055.01161497726</v>
+        <v>46055.01925098618</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <v>46055.01925238226</v>
       </c>
     </row>
     <row r="13">
@@ -2073,23 +2026,23 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>第2世（配）</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -2102,19 +2055,20 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
         <v>12</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X13" s="1" t="n">
-        <v>46055.01161498925</v>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>46055.01161498935</v>
+        <v>46055.01925099759</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <v>46055.01925238829</v>
       </c>
     </row>
     <row r="14">
@@ -2126,23 +2080,23 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>第2世（配）</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -2155,19 +2109,20 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
         <v>13</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X14" s="1" t="n">
-        <v>46055.01161500181</v>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y14" s="1" t="n">
-        <v>46055.01161500221</v>
+        <v>46055.01925101499</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>46055.01925239427</v>
       </c>
     </row>
     <row r="15">
@@ -2179,23 +2134,23 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>第2世（配）</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2208,19 +2163,20 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
         <v>14</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X15" s="1" t="n">
-        <v>46055.01161501917</v>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y15" s="1" t="n">
-        <v>46055.01161501929</v>
+        <v>46055.01925102668</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>46055.01925240012</v>
       </c>
     </row>
     <row r="16">
@@ -2232,23 +2188,23 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>第2世（配）</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -2261,19 +2217,20 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
         <v>15</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X16" s="1" t="n">
-        <v>46055.01161503369</v>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>46055.01161503383</v>
+        <v>46055.01925104101</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>46055.0192524069</v>
       </c>
     </row>
     <row r="17">
@@ -2285,23 +2242,23 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>第2世（配）</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -2314,19 +2271,20 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
         <v>16</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X17" s="1" t="n">
-        <v>46055.01161504533</v>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>46055.01161504542</v>
+        <v>46055.01925105489</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>46055.01925241513</v>
       </c>
     </row>
     <row r="18">
@@ -2338,23 +2296,23 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>第2世（配）</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -2367,19 +2325,20 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
         <v>17</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X18" s="1" t="n">
-        <v>46055.01161505622</v>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>46055.01161505628</v>
+        <v>46055.01925107157</v>
+      </c>
+      <c r="Z18" s="1" t="n">
+        <v>46055.01925242156</v>
       </c>
     </row>
     <row r="19">
@@ -2391,23 +2350,23 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>第2世（配）</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -2420,19 +2379,20 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
         <v>18</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X19" s="1" t="n">
-        <v>46055.01161506663</v>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y19" s="1" t="n">
-        <v>46055.0116150667</v>
+        <v>46055.01925108481</v>
+      </c>
+      <c r="Z19" s="1" t="n">
+        <v>46055.01925242738</v>
       </c>
     </row>
     <row r="20">
@@ -2444,28 +2404,28 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>3</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>法海公</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2477,19 +2437,20 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="n">
         <v>19</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X20" s="1" t="n">
-        <v>46055.01161507689</v>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>46055.01161507695</v>
+        <v>46055.019251096</v>
+      </c>
+      <c r="Z20" s="1" t="n">
+        <v>46055.01925243439</v>
       </c>
     </row>
     <row r="21">
@@ -2501,28 +2462,28 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>3</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>淮海公</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -2534,19 +2495,20 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
         <v>20</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X21" s="1" t="n">
-        <v>46055.01161508739</v>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>46055.01161508745</v>
+        <v>46055.01925110692</v>
+      </c>
+      <c r="Z21" s="1" t="n">
+        <v>46055.01925244127</v>
       </c>
     </row>
     <row r="22">
@@ -2558,28 +2520,28 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>淮海公</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
@@ -2591,19 +2553,20 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="n">
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
         <v>21</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X22" s="1" t="n">
-        <v>46055.01161509737</v>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>46055.01161509744</v>
+        <v>46055.01925112131</v>
+      </c>
+      <c r="Z22" s="1" t="n">
+        <v>46055.01925244716</v>
       </c>
     </row>
     <row r="23">
@@ -2615,28 +2578,28 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>3</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>得成公</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -2648,19 +2611,20 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="n">
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
         <v>22</v>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X23" s="1" t="n">
-        <v>46055.01161510908</v>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>46055.01161510916</v>
+        <v>46055.01925113449</v>
+      </c>
+      <c r="Z23" s="1" t="n">
+        <v>46055.01925245927</v>
       </c>
     </row>
     <row r="24">
@@ -2672,28 +2636,28 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
         <v>3</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>得成公</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -2705,19 +2669,20 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="n">
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
         <v>23</v>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X24" s="1" t="n">
-        <v>46055.01161512099</v>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>46055.01161512113</v>
+        <v>46055.01925114923</v>
+      </c>
+      <c r="Z24" s="1" t="n">
+        <v>46055.01925246768</v>
       </c>
     </row>
     <row r="25">
@@ -2729,28 +2694,28 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>千一公</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -2762,19 +2727,20 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="n">
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
         <v>24</v>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X25" s="1" t="n">
-        <v>46055.01161513197</v>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>46055.01161513205</v>
+        <v>46055.01925116013</v>
+      </c>
+      <c r="Z25" s="1" t="n">
+        <v>46055.01925247376</v>
       </c>
     </row>
     <row r="26">
@@ -2786,28 +2752,28 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>满海公</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2819,19 +2785,20 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="n">
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
         <v>25</v>
       </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X26" s="1" t="n">
-        <v>46055.01161514282</v>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>46055.0116151429</v>
+        <v>46055.01925117066</v>
+      </c>
+      <c r="Z26" s="1" t="n">
+        <v>46055.01925247986</v>
       </c>
     </row>
     <row r="27">
@@ -2843,28 +2810,28 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
         <v>3</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>满海公</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -2876,19 +2843,20 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="n">
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
         <v>26</v>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X27" s="1" t="n">
-        <v>46055.01161515379</v>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y27" s="1" t="n">
-        <v>46055.01161515387</v>
+        <v>46055.01925118142</v>
+      </c>
+      <c r="Z27" s="1" t="n">
+        <v>46055.01925248598</v>
       </c>
     </row>
     <row r="28">
@@ -2900,28 +2868,28 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
         <v>3</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>满海公</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -2933,19 +2901,20 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="n">
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
         <v>27</v>
       </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X28" s="1" t="n">
-        <v>46055.01161516441</v>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>46055.01161516448</v>
+        <v>46055.01925119365</v>
+      </c>
+      <c r="Z28" s="1" t="n">
+        <v>46055.01925249195</v>
       </c>
     </row>
     <row r="29">
@@ -2957,28 +2926,28 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>3</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>满海公</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -2990,19 +2959,20 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="n">
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
         <v>28</v>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X29" s="1" t="n">
-        <v>46055.01161517498</v>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>46055.01161517505</v>
+        <v>46055.01925120889</v>
+      </c>
+      <c r="Z29" s="1" t="n">
+        <v>46055.01925249795</v>
       </c>
     </row>
     <row r="30">
@@ -3014,28 +2984,28 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
         <v>3</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>第3世</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>满海公</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -3047,19 +3017,20 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="n">
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
         <v>29</v>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X30" s="1" t="n">
-        <v>46055.01161518632</v>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>46055.0116151864</v>
+        <v>46055.01925122301</v>
+      </c>
+      <c r="Z30" s="1" t="n">
+        <v>46055.0192525047</v>
       </c>
     </row>
     <row r="31">
@@ -3071,23 +3042,23 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
         <v>3</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>第3世（配）</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -3100,19 +3071,20 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="n">
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="n">
         <v>30</v>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X31" s="1" t="n">
-        <v>46055.01161519768</v>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>46055.01161519776</v>
+        <v>46055.01925123446</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <v>46055.01925251129</v>
       </c>
     </row>
     <row r="32">
@@ -3124,23 +3096,23 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>3</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>第3世（配）</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -3153,19 +3125,20 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="n">
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="n">
         <v>33</v>
       </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X32" s="1" t="n">
-        <v>46055.01161521889</v>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>46055.01161521903</v>
+        <v>46055.0192512461</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <v>46055.01925251731</v>
       </c>
     </row>
     <row r="33">
@@ -3177,23 +3150,23 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
         <v>3</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>第3世（配）</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -3206,19 +3179,20 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="n">
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="n">
         <v>34</v>
       </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X33" s="1" t="n">
-        <v>46055.01161523361</v>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>46055.01161523374</v>
+        <v>46055.01925125819</v>
+      </c>
+      <c r="Z33" s="1" t="n">
+        <v>46055.01925252347</v>
       </c>
     </row>
     <row r="34">
@@ -3230,23 +3204,23 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
         <v>3</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>第3世（配）</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -3259,19 +3233,20 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="n">
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="n">
         <v>35</v>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X34" s="1" t="n">
-        <v>46055.01161524632</v>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>46055.01161524641</v>
+        <v>46055.01925126877</v>
+      </c>
+      <c r="Z34" s="1" t="n">
+        <v>46055.01925252946</v>
       </c>
     </row>
     <row r="35">
@@ -3283,23 +3258,23 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
         <v>3</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>第3世（配）</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -3312,19 +3287,20 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="n">
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="n">
         <v>36</v>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X35" s="1" t="n">
-        <v>46055.01161525757</v>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>46055.01161525765</v>
+        <v>46055.01925127993</v>
+      </c>
+      <c r="Z35" s="1" t="n">
+        <v>46055.01925254123</v>
       </c>
     </row>
     <row r="36">
@@ -3336,23 +3312,23 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
         <v>3</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>第3世（配）</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -3365,19 +3341,20 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="n">
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="n">
         <v>37</v>
       </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X36" s="1" t="n">
-        <v>46055.0116152691</v>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>46055.01161526918</v>
+        <v>46055.01925129126</v>
+      </c>
+      <c r="Z36" s="1" t="n">
+        <v>46055.01925254713</v>
       </c>
     </row>
     <row r="37">
@@ -3389,23 +3366,23 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>3</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>第3世（配）</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -3418,19 +3395,20 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="n">
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="n">
         <v>39</v>
       </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X37" s="1" t="n">
-        <v>46055.01161528591</v>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>46055.01161528599</v>
+        <v>46055.01925130174</v>
+      </c>
+      <c r="Z37" s="1" t="n">
+        <v>46055.01925255316</v>
       </c>
     </row>
     <row r="38">
@@ -3442,23 +3420,23 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>3</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>第3世（配）</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -3471,19 +3449,20 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="n">
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="n">
         <v>40</v>
       </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X38" s="1" t="n">
-        <v>46055.01161529888</v>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>46055.01161529895</v>
+        <v>46055.01925131493</v>
+      </c>
+      <c r="Z38" s="1" t="n">
+        <v>46055.01925255924</v>
       </c>
     </row>
     <row r="39">
@@ -3499,28 +3478,28 @@
           <t>法行</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>第4世</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>法聪公</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -3532,19 +3511,20 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="n">
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="n">
         <v>44</v>
       </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X39" s="1" t="n">
-        <v>46055.01161532186</v>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>46055.01161532192</v>
+        <v>46055.01925133015</v>
+      </c>
+      <c r="Z39" s="1" t="n">
+        <v>46055.01925256544</v>
       </c>
     </row>
     <row r="40">
@@ -3556,28 +3536,28 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>第4世</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>法聪公</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -3589,19 +3569,20 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="n">
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="n">
         <v>45</v>
       </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X40" s="1" t="n">
-        <v>46055.01161533472</v>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>46055.01161533481</v>
+        <v>46055.01925134153</v>
+      </c>
+      <c r="Z40" s="1" t="n">
+        <v>46055.01925257225</v>
       </c>
     </row>
     <row r="41">
@@ -3617,28 +3598,28 @@
           <t>法瑄</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
         <v>4</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>第4世</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>法聪公</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -3650,19 +3631,20 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="n">
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="n">
         <v>46</v>
       </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X41" s="1" t="n">
-        <v>46055.01161534745</v>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>46055.01161534755</v>
+        <v>46055.01925135241</v>
+      </c>
+      <c r="Z41" s="1" t="n">
+        <v>46055.01925257893</v>
       </c>
     </row>
     <row r="42">
@@ -3674,28 +3656,28 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
         <v>4</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>第4世</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>法聪公</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -3707,19 +3689,20 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="n">
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="n">
         <v>47</v>
       </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X42" s="1" t="n">
-        <v>46055.01161535883</v>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>46055.01161535893</v>
+        <v>46055.01925136334</v>
+      </c>
+      <c r="Z42" s="1" t="n">
+        <v>46055.01925258608</v>
       </c>
     </row>
     <row r="43">
@@ -3731,28 +3714,28 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
         <v>4</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>第4世</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>法聪公</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -3764,19 +3747,20 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="n">
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="n">
         <v>48</v>
       </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X43" s="1" t="n">
-        <v>46055.01161537186</v>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>46055.01161537196</v>
+        <v>46055.01925137471</v>
+      </c>
+      <c r="Z43" s="1" t="n">
+        <v>46055.01925259399</v>
       </c>
     </row>
     <row r="44">
@@ -3788,23 +3772,23 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
         <v>4</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>第4世（配）</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -3817,19 +3801,20 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="n">
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="n">
         <v>49</v>
       </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X44" s="1" t="n">
-        <v>46055.01161538632</v>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>46055.01161538642</v>
+        <v>46055.01925139359</v>
+      </c>
+      <c r="Z44" s="1" t="n">
+        <v>46055.01925260104</v>
       </c>
     </row>
     <row r="45">
@@ -3841,23 +3826,23 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
         <v>4</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>第4世（配）</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -3870,19 +3855,20 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="n">
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="n">
         <v>50</v>
       </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X45" s="1" t="n">
-        <v>46055.01161540036</v>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>46055.01161540051</v>
+        <v>46055.01925140677</v>
+      </c>
+      <c r="Z45" s="1" t="n">
+        <v>46055.01925260724</v>
       </c>
     </row>
     <row r="46">
@@ -3894,23 +3880,23 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
         <v>4</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>第4世（配）</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -3923,19 +3909,20 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="n">
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="n">
         <v>51</v>
       </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X46" s="1" t="n">
-        <v>46055.01161541266</v>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>46055.01161541273</v>
+        <v>46055.01925141763</v>
+      </c>
+      <c r="Z46" s="1" t="n">
+        <v>46055.01925261365</v>
       </c>
     </row>
     <row r="47">
@@ -3951,28 +3938,28 @@
           <t>刘宽</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
         <v>5</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>第5世</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>忡瑛公</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -3984,19 +3971,20 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="n">
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="n">
         <v>52</v>
       </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X47" s="1" t="n">
-        <v>46055.01161542329</v>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>46055.01161542335</v>
+        <v>46055.01925143001</v>
+      </c>
+      <c r="Z47" s="1" t="n">
+        <v>46055.01925261992</v>
       </c>
     </row>
     <row r="48">
@@ -4012,28 +4000,28 @@
           <t>刘鑑</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
         <v>5</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>第5世</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>忡瑛公</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -4045,19 +4033,20 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="n">
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="n">
         <v>53</v>
       </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X48" s="1" t="n">
-        <v>46055.01161543378</v>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>46055.01161543384</v>
+        <v>46055.01925144469</v>
+      </c>
+      <c r="Z48" s="1" t="n">
+        <v>46055.01925262668</v>
       </c>
     </row>
     <row r="49">
@@ -4073,28 +4062,28 @@
           <t>海开</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
         <v>5</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>第5世</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>忡瑄公</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
@@ -4106,19 +4095,20 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="n">
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="n">
         <v>54</v>
       </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X49" s="1" t="n">
-        <v>46055.01161544481</v>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y49" s="1" t="n">
-        <v>46055.01161544492</v>
+        <v>46055.01925145899</v>
+      </c>
+      <c r="Z49" s="1" t="n">
+        <v>46055.01925263261</v>
       </c>
     </row>
     <row r="50">
@@ -4130,28 +4120,28 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
         <v>5</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>第5世</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>忡渊公</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -4163,19 +4153,20 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="n">
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="n">
         <v>55</v>
       </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X50" s="1" t="n">
-        <v>46055.01161545623</v>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>46055.01161545629</v>
+        <v>46055.01925146944</v>
+      </c>
+      <c r="Z50" s="1" t="n">
+        <v>46055.01925263969</v>
       </c>
     </row>
     <row r="51">
@@ -4187,28 +4178,28 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
         <v>5</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>第5世</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>忡渊公</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -4220,19 +4211,20 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="n">
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="n">
         <v>56</v>
       </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X51" s="1" t="n">
-        <v>46055.01161546718</v>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>46055.01161546724</v>
+        <v>46055.01925148018</v>
+      </c>
+      <c r="Z51" s="1" t="n">
+        <v>46055.01925264578</v>
       </c>
     </row>
     <row r="52">
@@ -4244,28 +4236,28 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F52" t="b">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
         <v>5</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>第5世</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>忡渊公</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -4277,19 +4269,20 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="n">
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="n">
         <v>57</v>
       </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X52" s="1" t="n">
-        <v>46055.01161547788</v>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>46055.01161547795</v>
+        <v>46055.0192514908</v>
+      </c>
+      <c r="Z52" s="1" t="n">
+        <v>46055.01925265201</v>
       </c>
     </row>
     <row r="53">
@@ -4301,28 +4294,28 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F53" t="b">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
         <v>5</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>第5世</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>忡渊公</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -4334,19 +4327,20 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="n">
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="n">
         <v>58</v>
       </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X53" s="1" t="n">
-        <v>46055.01161548943</v>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>46055.01161548951</v>
+        <v>46055.01925150184</v>
+      </c>
+      <c r="Z53" s="1" t="n">
+        <v>46055.01925265853</v>
       </c>
     </row>
     <row r="54">
@@ -4358,28 +4352,28 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F54" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
         <v>5</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>第5世</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>忡璵公</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -4391,19 +4385,20 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="n">
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="n">
         <v>59</v>
       </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X54" s="1" t="n">
-        <v>46055.01161550081</v>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>46055.01161550089</v>
+        <v>46055.01925151303</v>
+      </c>
+      <c r="Z54" s="1" t="n">
+        <v>46055.01925266447</v>
       </c>
     </row>
     <row r="55">
@@ -4415,28 +4410,28 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F55" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
         <v>5</v>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>第5世</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>忡璵公</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -4448,19 +4443,20 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="n">
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="n">
         <v>60</v>
       </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X55" s="1" t="n">
-        <v>46055.01161551195</v>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>46055.01161551203</v>
+        <v>46055.01925152611</v>
+      </c>
+      <c r="Z55" s="1" t="n">
+        <v>46055.01925267075</v>
       </c>
     </row>
     <row r="56">
@@ -4472,23 +4468,23 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F56" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
         <v>5</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>第5世（配）</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -4501,19 +4497,20 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="n">
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="n">
         <v>61</v>
       </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X56" s="1" t="n">
-        <v>46055.01161552323</v>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>46055.0116155233</v>
+        <v>46055.01925154237</v>
+      </c>
+      <c r="Z56" s="1" t="n">
+        <v>46055.01925267759</v>
       </c>
     </row>
     <row r="57">
@@ -4529,28 +4526,28 @@
           <t>法辉</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F57" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
         <v>6</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>法宽公</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
@@ -4562,19 +4559,20 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="n">
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="n">
         <v>65</v>
       </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X57" s="1" t="n">
-        <v>46055.01161554702</v>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>46055.0116155471</v>
+        <v>46055.01925155643</v>
+      </c>
+      <c r="Z57" s="1" t="n">
+        <v>46055.0192526842</v>
       </c>
     </row>
     <row r="58">
@@ -4590,28 +4588,28 @@
           <t>刘鸾</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F58" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
         <v>6</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>法宽公</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -4623,19 +4621,20 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="n">
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="n">
         <v>66</v>
       </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X58" s="1" t="n">
-        <v>46055.01161555934</v>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>46055.01161555941</v>
+        <v>46055.01925157125</v>
+      </c>
+      <c r="Z58" s="1" t="n">
+        <v>46055.0192526907</v>
       </c>
     </row>
     <row r="59">
@@ -4647,28 +4646,28 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F59" t="b">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
         <v>6</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>法猷公</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
@@ -4680,19 +4679,20 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="n">
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="n">
         <v>67</v>
       </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X59" s="1" t="n">
-        <v>46055.01161557026</v>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>46055.01161557032</v>
+        <v>46055.01925158219</v>
+      </c>
+      <c r="Z59" s="1" t="n">
+        <v>46055.01925269655</v>
       </c>
     </row>
     <row r="60">
@@ -4708,28 +4708,28 @@
           <t>法珍、玲</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F60" t="b">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
         <v>6</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>法猷公</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
@@ -4741,19 +4741,20 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="n">
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="n">
         <v>68</v>
       </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X60" s="1" t="n">
-        <v>46055.01161558134</v>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>46055.01161558142</v>
+        <v>46055.01925159305</v>
+      </c>
+      <c r="Z60" s="1" t="n">
+        <v>46055.01925270235</v>
       </c>
     </row>
     <row r="61">
@@ -4769,28 +4770,28 @@
           <t>法高</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F61" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
         <v>6</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>法猷公</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -4802,19 +4803,20 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="n">
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="n">
         <v>69</v>
       </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X61" s="1" t="n">
-        <v>46055.01161559308</v>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>46055.01161559315</v>
+        <v>46055.01925160469</v>
+      </c>
+      <c r="Z61" s="1" t="n">
+        <v>46055.0192527082</v>
       </c>
     </row>
     <row r="62">
@@ -4826,28 +4828,28 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F62" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
         <v>6</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>法猷公</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -4859,19 +4861,20 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="n">
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="n">
         <v>70</v>
       </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X62" s="1" t="n">
-        <v>46055.01161560592</v>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>46055.01161560602</v>
+        <v>46055.01925161539</v>
+      </c>
+      <c r="Z62" s="1" t="n">
+        <v>46055.019252715</v>
       </c>
     </row>
     <row r="63">
@@ -4887,28 +4890,28 @@
           <t>法璉</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F63" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
         <v>6</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>法猷公</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -4920,19 +4923,20 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="n">
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="n">
         <v>71</v>
       </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X63" s="1" t="n">
-        <v>46055.01161562102</v>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>46055.01161562114</v>
+        <v>46055.01925162969</v>
+      </c>
+      <c r="Z63" s="1" t="n">
+        <v>46055.01925272168</v>
       </c>
     </row>
     <row r="64">
@@ -4944,28 +4948,28 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F64" t="b">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
         <v>6</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>法猷公</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
@@ -4977,19 +4981,20 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="n">
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="n">
         <v>72</v>
       </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X64" s="1" t="n">
-        <v>46055.01161563447</v>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>46055.01161563456</v>
+        <v>46055.01925164102</v>
+      </c>
+      <c r="Z64" s="1" t="n">
+        <v>46055.01925273034</v>
       </c>
     </row>
     <row r="65">
@@ -5005,28 +5010,28 @@
           <t>法瑀</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F65" t="b">
-        <v>0</v>
-      </c>
-      <c r="G65" t="n">
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
         <v>6</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>法猷公</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -5038,19 +5043,20 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="n">
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="n">
         <v>73</v>
       </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X65" s="1" t="n">
-        <v>46055.01161564721</v>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y65" s="1" t="n">
-        <v>46055.0116156474</v>
+        <v>46055.01925165165</v>
+      </c>
+      <c r="Z65" s="1" t="n">
+        <v>46055.01925273795</v>
       </c>
     </row>
     <row r="66">
@@ -5066,28 +5072,28 @@
           <t>法珦</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F66" t="b">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
         <v>6</v>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>法猷公</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
@@ -5099,19 +5105,20 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="n">
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="n">
         <v>74</v>
       </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X66" s="1" t="n">
-        <v>46055.01161565968</v>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y66" s="1" t="n">
-        <v>46055.01161565977</v>
+        <v>46055.01925166242</v>
+      </c>
+      <c r="Z66" s="1" t="n">
+        <v>46055.01925275093</v>
       </c>
     </row>
     <row r="67">
@@ -5123,28 +5130,28 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F67" t="b">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
         <v>6</v>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>法开公</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -5156,19 +5163,20 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="n">
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="n">
         <v>75</v>
       </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X67" s="1" t="n">
-        <v>46055.01161567252</v>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y67" s="1" t="n">
-        <v>46055.01161567264</v>
+        <v>46055.01925167636</v>
+      </c>
+      <c r="Z67" s="1" t="n">
+        <v>46055.01925275851</v>
       </c>
     </row>
     <row r="68">
@@ -5184,28 +5192,28 @@
           <t>蒲郎、横雅</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F68" t="b">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
         <v>6</v>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>第6世</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>法开公</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -5217,19 +5225,20 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="n">
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="n">
         <v>76</v>
       </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X68" s="1" t="n">
-        <v>46055.01161568672</v>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y68" s="1" t="n">
-        <v>46055.01161568682</v>
+        <v>46055.01925168873</v>
+      </c>
+      <c r="Z68" s="1" t="n">
+        <v>46055.01925276447</v>
       </c>
     </row>
     <row r="69">
@@ -5241,23 +5250,23 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F69" t="b">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
         <v>6</v>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>第6世（配）</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
@@ -5270,19 +5279,20 @@
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="n">
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="n">
         <v>77</v>
       </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X69" s="1" t="n">
-        <v>46055.01161570159</v>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y69" s="1" t="n">
-        <v>46055.01161570173</v>
+        <v>46055.01925169981</v>
+      </c>
+      <c r="Z69" s="1" t="n">
+        <v>46055.01925277039</v>
       </c>
     </row>
     <row r="70">
@@ -5294,23 +5304,23 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F70" t="b">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
         <v>6</v>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>第6世（配）</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
@@ -5323,19 +5333,20 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="n">
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="n">
         <v>78</v>
       </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X70" s="1" t="n">
-        <v>46055.01161571385</v>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y70" s="1" t="n">
-        <v>46055.01161571392</v>
+        <v>46055.01925171058</v>
+      </c>
+      <c r="Z70" s="1" t="n">
+        <v>46055.01925277647</v>
       </c>
     </row>
     <row r="71">
@@ -5347,23 +5358,23 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F71" t="b">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
         <v>6</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>第6世（配）</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
@@ -5376,19 +5387,20 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="n">
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="n">
         <v>81</v>
       </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X71" s="1" t="n">
-        <v>46055.01161573445</v>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y71" s="1" t="n">
-        <v>46055.01161573455</v>
+        <v>46055.01925172078</v>
+      </c>
+      <c r="Z71" s="1" t="n">
+        <v>46055.01925278285</v>
       </c>
     </row>
     <row r="72">
@@ -5400,23 +5412,23 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F72" t="b">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
         <v>6</v>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>第6世（配）</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
@@ -5429,19 +5441,20 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="n">
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="n">
         <v>82</v>
       </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X72" s="1" t="n">
-        <v>46055.01161574803</v>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y72" s="1" t="n">
-        <v>46055.01161574816</v>
+        <v>46055.01925173347</v>
+      </c>
+      <c r="Z72" s="1" t="n">
+        <v>46055.01925278883</v>
       </c>
     </row>
     <row r="73">
@@ -5453,23 +5466,23 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F73" t="b">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
         <v>6</v>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>第6世（配）</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
@@ -5482,19 +5495,20 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="n">
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="n">
         <v>86</v>
       </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X73" s="1" t="n">
-        <v>46055.01161577408</v>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y73" s="1" t="n">
-        <v>46055.01161577418</v>
+        <v>46055.01925174412</v>
+      </c>
+      <c r="Z73" s="1" t="n">
+        <v>46055.01925279533</v>
       </c>
     </row>
     <row r="74">
@@ -5506,23 +5520,23 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F74" t="b">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
         <v>16</v>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>第16世</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
@@ -5535,19 +5549,20 @@
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="n">
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="n">
         <v>87</v>
       </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X74" s="1" t="n">
-        <v>46055.0116157868</v>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y74" s="1" t="n">
-        <v>46055.0116157869</v>
+        <v>46055.01925175585</v>
+      </c>
+      <c r="Z74" s="1" t="n">
+        <v>46055.01925280334</v>
       </c>
     </row>
     <row r="75">
@@ -5559,23 +5574,23 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F75" t="b">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
+      <c r="G75" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
         <v>16</v>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>第16世（配）</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
@@ -5588,19 +5603,20 @@
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="n">
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="n">
         <v>88</v>
       </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X75" s="1" t="n">
-        <v>46055.01161579842</v>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y75" s="1" t="n">
-        <v>46055.01161579851</v>
+        <v>46055.01925177076</v>
+      </c>
+      <c r="Z75" s="1" t="n">
+        <v>46055.01925281037</v>
       </c>
     </row>
     <row r="76">
@@ -5612,33 +5628,33 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F76" t="b">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
         <v>17</v>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>第17世</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>魁柏公</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>吴氏</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
@@ -5649,19 +5665,20 @@
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
-      <c r="V76" t="n">
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="n">
         <v>89</v>
       </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X76" s="1" t="n">
-        <v>46055.01161580965</v>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y76" s="1" t="n">
-        <v>46055.01161580972</v>
+        <v>46055.01925178412</v>
+      </c>
+      <c r="Z76" s="1" t="n">
+        <v>46055.01925281755</v>
       </c>
     </row>
     <row r="77">
@@ -5673,33 +5690,33 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F77" t="b">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
         <v>17</v>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>第17世</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>魁柏公</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>吴氏</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
@@ -5710,19 +5727,20 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="n">
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="n">
         <v>90</v>
       </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X77" s="1" t="n">
-        <v>46055.01161582117</v>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y77" s="1" t="n">
-        <v>46055.01161582125</v>
+        <v>46055.01925179992</v>
+      </c>
+      <c r="Z77" s="1" t="n">
+        <v>46055.01925282864</v>
       </c>
     </row>
     <row r="78">
@@ -5734,33 +5752,33 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F78" t="b">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
         <v>17</v>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>第17世</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>魁柏公</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>吴氏</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
@@ -5771,19 +5789,20 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="n">
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="n">
         <v>91</v>
       </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X78" s="1" t="n">
-        <v>46055.0116158347</v>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y78" s="1" t="n">
-        <v>46055.01161583478</v>
+        <v>46055.01925181118</v>
+      </c>
+      <c r="Z78" s="1" t="n">
+        <v>46055.01925283616</v>
       </c>
     </row>
     <row r="79">
@@ -5795,28 +5814,28 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F79" t="b">
-        <v>0</v>
-      </c>
-      <c r="G79" t="n">
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
         <v>18</v>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>第18世</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>粤盛</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
@@ -5828,19 +5847,20 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
-      <c r="V79" t="n">
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="n">
         <v>92</v>
       </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X79" s="1" t="n">
-        <v>46055.0116158489</v>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y79" s="1" t="n">
-        <v>46055.01161584901</v>
+        <v>46055.01925182248</v>
+      </c>
+      <c r="Z79" s="1" t="n">
+        <v>46055.01925284333</v>
       </c>
     </row>
     <row r="80">
@@ -5852,28 +5872,28 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F80" t="b">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
         <v>18</v>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>第18世</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>粤兴</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
@@ -5885,19 +5905,20 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
-      <c r="V80" t="n">
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="n">
         <v>93</v>
       </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X80" s="1" t="n">
-        <v>46055.01161586184</v>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y80" s="1" t="n">
-        <v>46055.01161586194</v>
+        <v>46055.01925183326</v>
+      </c>
+      <c r="Z80" s="1" t="n">
+        <v>46055.01925285024</v>
       </c>
     </row>
     <row r="81">
@@ -5909,28 +5930,28 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F81" t="b">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
+      <c r="G81" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
         <v>18</v>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>第18世</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>粤桂</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
@@ -5942,19 +5963,20 @@
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="n">
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="n">
         <v>94</v>
       </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X81" s="1" t="n">
-        <v>46055.01161587297</v>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y81" s="1" t="n">
-        <v>46055.01161587305</v>
+        <v>46055.0192518446</v>
+      </c>
+      <c r="Z81" s="1" t="n">
+        <v>46055.01925285732</v>
       </c>
     </row>
     <row r="82">
@@ -5966,28 +5988,28 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F82" t="b">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
+      <c r="G82" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
         <v>19</v>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>第19世</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>彩光</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
@@ -5999,19 +6021,20 @@
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
-      <c r="V82" t="n">
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="n">
         <v>95</v>
       </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X82" s="1" t="n">
-        <v>46055.01161588414</v>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y82" s="1" t="n">
-        <v>46055.0116158842</v>
+        <v>46055.01925185521</v>
+      </c>
+      <c r="Z82" s="1" t="n">
+        <v>46055.01925286412</v>
       </c>
     </row>
     <row r="83">
@@ -6023,28 +6046,28 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F83" t="b">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
+      <c r="G83" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
         <v>19</v>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>第19世</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>彩光</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
@@ -6056,19 +6079,20 @@
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
-      <c r="V83" t="n">
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="n">
         <v>96</v>
       </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X83" s="1" t="n">
-        <v>46055.01161589421</v>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y83" s="1" t="n">
-        <v>46055.01161589428</v>
+        <v>46055.01925186651</v>
+      </c>
+      <c r="Z83" s="1" t="n">
+        <v>46055.01925287331</v>
       </c>
     </row>
     <row r="84">
@@ -6080,28 +6104,28 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F84" t="b">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
+      <c r="G84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
         <v>19</v>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>第19世</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>彩光</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
@@ -6113,19 +6137,20 @@
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="n">
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="n">
         <v>97</v>
       </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X84" s="1" t="n">
-        <v>46055.0116159048</v>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y84" s="1" t="n">
-        <v>46055.01161590486</v>
+        <v>46055.01925187706</v>
+      </c>
+      <c r="Z84" s="1" t="n">
+        <v>46055.01925287966</v>
       </c>
     </row>
     <row r="85">
@@ -6137,28 +6162,28 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F85" t="b">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
+      <c r="G85" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
         <v>19</v>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>第19世</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>彩芹</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
@@ -6170,19 +6195,20 @@
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="n">
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="n">
         <v>98</v>
       </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X85" s="1" t="n">
-        <v>46055.01161591546</v>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y85" s="1" t="n">
-        <v>46055.01161591557</v>
+        <v>46055.01925188771</v>
+      </c>
+      <c r="Z85" s="1" t="n">
+        <v>46055.0192528863</v>
       </c>
     </row>
     <row r="86">
@@ -6194,28 +6220,28 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F86" t="b">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
         <v>19</v>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>第19世</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>彩芹</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
@@ -6227,19 +6253,20 @@
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
-      <c r="V86" t="n">
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="n">
         <v>99</v>
       </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X86" s="1" t="n">
-        <v>46055.01161592636</v>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y86" s="1" t="n">
-        <v>46055.01161592642</v>
+        <v>46055.01925189815</v>
+      </c>
+      <c r="Z86" s="1" t="n">
+        <v>46055.01925289314</v>
       </c>
     </row>
     <row r="87">
@@ -6251,28 +6278,28 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F87" t="b">
-        <v>0</v>
-      </c>
-      <c r="G87" t="n">
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
         <v>19</v>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>第19世</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>彩芹</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
@@ -6284,19 +6311,20 @@
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
-      <c r="V87" t="n">
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="n">
         <v>100</v>
       </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X87" s="1" t="n">
-        <v>46055.01161593843</v>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y87" s="1" t="n">
-        <v>46055.01161593852</v>
+        <v>46055.01925190871</v>
+      </c>
+      <c r="Z87" s="1" t="n">
+        <v>46055.01925290019</v>
       </c>
     </row>
     <row r="88">
@@ -6308,28 +6336,28 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F88" t="b">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
+      <c r="G88" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
         <v>19</v>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>第19世</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>彩椿</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
@@ -6341,19 +6369,20 @@
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
-      <c r="V88" t="n">
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="n">
         <v>101</v>
       </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X88" s="1" t="n">
-        <v>46055.01161594957</v>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y88" s="1" t="n">
-        <v>46055.01161594964</v>
+        <v>46055.01925192027</v>
+      </c>
+      <c r="Z88" s="1" t="n">
+        <v>46055.01925290778</v>
       </c>
     </row>
     <row r="89">
@@ -6365,28 +6394,28 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F89" t="b">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
+      <c r="G89" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
         <v>19</v>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>第19世</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>彩椿</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
@@ -6398,19 +6427,20 @@
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
-      <c r="V89" t="n">
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="n">
         <v>102</v>
       </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X89" s="1" t="n">
-        <v>46055.01161595998</v>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y89" s="1" t="n">
-        <v>46055.01161596004</v>
+        <v>46055.01925193134</v>
+      </c>
+      <c r="Z89" s="1" t="n">
+        <v>46055.01925291464</v>
       </c>
     </row>
     <row r="90">
@@ -6422,28 +6452,28 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F90" t="b">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
+      <c r="G90" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
         <v>19</v>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>第19世</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>彩椿</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
@@ -6455,19 +6485,20 @@
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
-      <c r="V90" t="n">
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="n">
         <v>103</v>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X90" s="1" t="n">
-        <v>46055.01161597206</v>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y90" s="1" t="n">
-        <v>46055.01161597214</v>
+        <v>46055.01925194223</v>
+      </c>
+      <c r="Z90" s="1" t="n">
+        <v>46055.01925292094</v>
       </c>
     </row>
     <row r="91">
@@ -6479,28 +6510,28 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F91" t="b">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
+      <c r="G91" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
         <v>20</v>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>昔元</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
@@ -6512,19 +6543,20 @@
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
-      <c r="V91" t="n">
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="n">
         <v>104</v>
       </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X91" s="1" t="n">
-        <v>46055.01161598404</v>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y91" s="1" t="n">
-        <v>46055.01161598412</v>
+        <v>46055.01925195282</v>
+      </c>
+      <c r="Z91" s="1" t="n">
+        <v>46055.01925292706</v>
       </c>
     </row>
     <row r="92">
@@ -6536,28 +6568,28 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F92" t="b">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
+      <c r="G92" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
         <v>20</v>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>昔元</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
@@ -6569,19 +6601,20 @@
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
-      <c r="V92" t="n">
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="n">
         <v>105</v>
       </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X92" s="1" t="n">
-        <v>46055.01161599558</v>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y92" s="1" t="n">
-        <v>46055.01161599565</v>
+        <v>46055.01925196385</v>
+      </c>
+      <c r="Z92" s="1" t="n">
+        <v>46055.01925293362</v>
       </c>
     </row>
     <row r="93">
@@ -6593,28 +6626,28 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F93" t="b">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
+      <c r="G93" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
         <v>20</v>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>昔泉</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
@@ -6626,19 +6659,20 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
-      <c r="V93" t="n">
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="n">
         <v>106</v>
       </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X93" s="1" t="n">
-        <v>46055.01161600663</v>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y93" s="1" t="n">
-        <v>46055.0116160067</v>
+        <v>46055.01925197507</v>
+      </c>
+      <c r="Z93" s="1" t="n">
+        <v>46055.01925294018</v>
       </c>
     </row>
     <row r="94">
@@ -6650,28 +6684,28 @@
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F94" t="b">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
+      <c r="G94" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
         <v>20</v>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>昔泉</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
@@ -6683,19 +6717,20 @@
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
-      <c r="V94" t="n">
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="n">
         <v>107</v>
       </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X94" s="1" t="n">
-        <v>46055.011616018</v>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y94" s="1" t="n">
-        <v>46055.01161601808</v>
+        <v>46055.01925198574</v>
+      </c>
+      <c r="Z94" s="1" t="n">
+        <v>46055.01925294704</v>
       </c>
     </row>
     <row r="95">
@@ -6707,28 +6742,28 @@
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F95" t="b">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
+      <c r="G95" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
         <v>20</v>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>昔仁</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
@@ -6740,19 +6775,20 @@
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
-      <c r="V95" t="n">
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="n">
         <v>108</v>
       </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X95" s="1" t="n">
-        <v>46055.01161602913</v>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y95" s="1" t="n">
-        <v>46055.0116160292</v>
+        <v>46055.01925199627</v>
+      </c>
+      <c r="Z95" s="1" t="n">
+        <v>46055.01925295409</v>
       </c>
     </row>
     <row r="96">
@@ -6764,28 +6800,28 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F96" t="b">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
+      <c r="G96" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>20</v>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>昔森</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
@@ -6797,19 +6833,20 @@
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
-      <c r="V96" t="n">
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="n">
         <v>109</v>
       </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X96" s="1" t="n">
-        <v>46055.01161604036</v>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y96" s="1" t="n">
-        <v>46055.01161604043</v>
+        <v>46055.01925200861</v>
+      </c>
+      <c r="Z96" s="1" t="n">
+        <v>46055.0192529613</v>
       </c>
     </row>
     <row r="97">
@@ -6821,28 +6858,28 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F97" t="b">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
+      <c r="G97" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>20</v>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>昔文</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
@@ -6854,19 +6891,20 @@
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
-      <c r="V97" t="n">
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="n">
         <v>110</v>
       </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X97" s="1" t="n">
-        <v>46055.0116160512</v>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y97" s="1" t="n">
-        <v>46055.01161605127</v>
+        <v>46055.01925202141</v>
+      </c>
+      <c r="Z97" s="1" t="n">
+        <v>46055.01925296812</v>
       </c>
     </row>
     <row r="98">
@@ -6878,28 +6916,28 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F98" t="b">
-        <v>0</v>
-      </c>
-      <c r="G98" t="n">
+      <c r="G98" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
         <v>20</v>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>昔义</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
@@ -6911,19 +6949,20 @@
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
-      <c r="V98" t="n">
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="n">
         <v>111</v>
       </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X98" s="1" t="n">
-        <v>46055.01161606478</v>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y98" s="1" t="n">
-        <v>46055.01161606488</v>
+        <v>46055.01925203264</v>
+      </c>
+      <c r="Z98" s="1" t="n">
+        <v>46055.01925297494</v>
       </c>
     </row>
     <row r="99">
@@ -6935,30 +6974,34 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F99" t="b">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
+      <c r="G99" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
         <v>20</v>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>昔战</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>法海公支系</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
@@ -6968,19 +7011,20 @@
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
-      <c r="V99" t="n">
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="n">
         <v>112</v>
       </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X99" s="1" t="n">
-        <v>46055.01161607795</v>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y99" s="1" t="n">
-        <v>46055.01161607808</v>
+        <v>46055.01925204371</v>
+      </c>
+      <c r="Z99" s="1" t="n">
+        <v>46055.25504283647</v>
       </c>
     </row>
     <row r="100">
@@ -6992,30 +7036,34 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F100" t="b">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
+      <c r="G100" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
         <v>20</v>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>昔民</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>法海公支系</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
@@ -7025,19 +7073,20 @@
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
-      <c r="V100" t="n">
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="n">
         <v>113</v>
       </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X100" s="1" t="n">
-        <v>46055.01161609066</v>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y100" s="1" t="n">
-        <v>46055.01161609074</v>
+        <v>46055.0192520553</v>
+      </c>
+      <c r="Z100" s="1" t="n">
+        <v>46055.25527462247</v>
       </c>
     </row>
     <row r="101">
@@ -7049,28 +7098,28 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F101" t="b">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
+      <c r="G101" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
         <v>20</v>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>昔炎</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
@@ -7082,19 +7131,20 @@
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
-      <c r="V101" t="n">
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="n">
         <v>114</v>
       </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X101" s="1" t="n">
-        <v>46055.01161610187</v>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y101" s="1" t="n">
-        <v>46055.01161610195</v>
+        <v>46055.01925206618</v>
+      </c>
+      <c r="Z101" s="1" t="n">
+        <v>46055.01925300333</v>
       </c>
     </row>
     <row r="102">
@@ -7106,28 +7156,28 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F102" t="b">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
+      <c r="G102" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
         <v>20</v>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>昔炎</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
@@ -7139,19 +7189,20 @@
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
-      <c r="V102" t="n">
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="n">
         <v>115</v>
       </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X102" s="1" t="n">
-        <v>46055.01161611352</v>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y102" s="1" t="n">
-        <v>46055.01161611365</v>
+        <v>46055.01925207693</v>
+      </c>
+      <c r="Z102" s="1" t="n">
+        <v>46055.01925301089</v>
       </c>
     </row>
     <row r="103">
@@ -7163,28 +7214,28 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F103" t="b">
-        <v>0</v>
-      </c>
-      <c r="G103" t="n">
+      <c r="G103" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
         <v>20</v>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>昔炎</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
@@ -7196,19 +7247,20 @@
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
-      <c r="V103" t="n">
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="n">
         <v>116</v>
       </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X103" s="1" t="n">
-        <v>46055.01161612618</v>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y103" s="1" t="n">
-        <v>46055.0116161263</v>
+        <v>46055.01925208933</v>
+      </c>
+      <c r="Z103" s="1" t="n">
+        <v>46055.01925302025</v>
       </c>
     </row>
     <row r="104">
@@ -7220,28 +7272,28 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F104" t="b">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
+      <c r="G104" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
         <v>20</v>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>昔炎</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
@@ -7253,19 +7305,20 @@
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
-      <c r="V104" t="n">
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="n">
         <v>117</v>
       </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X104" s="1" t="n">
-        <v>46055.01161613969</v>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y104" s="1" t="n">
-        <v>46055.01161613979</v>
+        <v>46055.01925210009</v>
+      </c>
+      <c r="Z104" s="1" t="n">
+        <v>46055.01925302801</v>
       </c>
     </row>
     <row r="105">
@@ -7277,28 +7330,28 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F105" t="b">
-        <v>0</v>
-      </c>
-      <c r="G105" t="n">
+      <c r="G105" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
         <v>20</v>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>昔炎</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
@@ -7310,19 +7363,20 @@
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
-      <c r="V105" t="n">
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="n">
         <v>118</v>
       </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X105" s="1" t="n">
-        <v>46055.01161615195</v>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y105" s="1" t="n">
-        <v>46055.01161615203</v>
+        <v>46055.01925211051</v>
+      </c>
+      <c r="Z105" s="1" t="n">
+        <v>46055.01925303542</v>
       </c>
     </row>
     <row r="106">
@@ -7334,28 +7388,28 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F106" t="b">
-        <v>0</v>
-      </c>
-      <c r="G106" t="n">
+      <c r="G106" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
         <v>20</v>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>昔炎</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
@@ -7367,19 +7421,20 @@
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
-      <c r="V106" t="n">
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="n">
         <v>119</v>
       </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X106" s="1" t="n">
-        <v>46055.01161616345</v>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y106" s="1" t="n">
-        <v>46055.01161616357</v>
+        <v>46055.01925212102</v>
+      </c>
+      <c r="Z106" s="1" t="n">
+        <v>46055.01925304274</v>
       </c>
     </row>
     <row r="107">
@@ -7391,28 +7446,28 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F107" t="b">
-        <v>0</v>
-      </c>
-      <c r="G107" t="n">
+      <c r="G107" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
         <v>20</v>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>第20世</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>昔炎</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
@@ -7424,19 +7479,20 @@
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
-      <c r="V107" t="n">
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="n">
         <v>120</v>
       </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="X107" s="1" t="n">
-        <v>46055.01161617443</v>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
       </c>
       <c r="Y107" s="1" t="n">
-        <v>46055.0116161745</v>
+        <v>46055.01925213189</v>
+      </c>
+      <c r="Z107" s="1" t="n">
+        <v>46055.0192530505</v>
       </c>
     </row>
   </sheetData>

--- a/genealogy_data.xlsx
+++ b/genealogy_data.xlsx
@@ -449,8 +449,10 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="b">
-        <v>0</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,8 +465,10 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="b">
-        <v>1</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -477,8 +481,10 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="b">
-        <v>0</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -491,8 +497,10 @@
       <c r="A5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="b">
-        <v>1</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -505,8 +513,10 @@
       <c r="A6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="b">
-        <v>0</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -519,8 +529,10 @@
       <c r="A7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="b">
-        <v>1</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -533,8 +545,10 @@
       <c r="A8" t="n">
         <v>4</v>
       </c>
-      <c r="B8" t="b">
-        <v>0</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -547,8 +561,10 @@
       <c r="A9" t="n">
         <v>4</v>
       </c>
-      <c r="B9" t="b">
-        <v>1</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -561,8 +577,10 @@
       <c r="A10" t="n">
         <v>5</v>
       </c>
-      <c r="B10" t="b">
-        <v>0</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -575,8 +593,10 @@
       <c r="A11" t="n">
         <v>5</v>
       </c>
-      <c r="B11" t="b">
-        <v>1</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -589,8 +609,10 @@
       <c r="A12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" t="b">
-        <v>0</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -603,8 +625,10 @@
       <c r="A13" t="n">
         <v>6</v>
       </c>
-      <c r="B13" t="b">
-        <v>1</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -617,8 +641,10 @@
       <c r="A14" t="n">
         <v>7</v>
       </c>
-      <c r="B14" t="b">
-        <v>0</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -631,8 +657,10 @@
       <c r="A15" t="n">
         <v>7</v>
       </c>
-      <c r="B15" t="b">
-        <v>1</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -645,8 +673,10 @@
       <c r="A16" t="n">
         <v>8</v>
       </c>
-      <c r="B16" t="b">
-        <v>0</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -659,8 +689,10 @@
       <c r="A17" t="n">
         <v>8</v>
       </c>
-      <c r="B17" t="b">
-        <v>1</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -673,8 +705,10 @@
       <c r="A18" t="n">
         <v>9</v>
       </c>
-      <c r="B18" t="b">
-        <v>0</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -687,8 +721,10 @@
       <c r="A19" t="n">
         <v>9</v>
       </c>
-      <c r="B19" t="b">
-        <v>1</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -701,8 +737,10 @@
       <c r="A20" t="n">
         <v>10</v>
       </c>
-      <c r="B20" t="b">
-        <v>0</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -715,8 +753,10 @@
       <c r="A21" t="n">
         <v>10</v>
       </c>
-      <c r="B21" t="b">
-        <v>1</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -729,8 +769,10 @@
       <c r="A22" t="n">
         <v>11</v>
       </c>
-      <c r="B22" t="b">
-        <v>0</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -743,8 +785,10 @@
       <c r="A23" t="n">
         <v>11</v>
       </c>
-      <c r="B23" t="b">
-        <v>1</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -757,8 +801,10 @@
       <c r="A24" t="n">
         <v>12</v>
       </c>
-      <c r="B24" t="b">
-        <v>0</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -771,8 +817,10 @@
       <c r="A25" t="n">
         <v>12</v>
       </c>
-      <c r="B25" t="b">
-        <v>1</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -785,8 +833,10 @@
       <c r="A26" t="n">
         <v>13</v>
       </c>
-      <c r="B26" t="b">
-        <v>0</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -799,8 +849,10 @@
       <c r="A27" t="n">
         <v>13</v>
       </c>
-      <c r="B27" t="b">
-        <v>1</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -813,8 +865,10 @@
       <c r="A28" t="n">
         <v>14</v>
       </c>
-      <c r="B28" t="b">
-        <v>0</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -827,8 +881,10 @@
       <c r="A29" t="n">
         <v>14</v>
       </c>
-      <c r="B29" t="b">
-        <v>1</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -841,8 +897,10 @@
       <c r="A30" t="n">
         <v>15</v>
       </c>
-      <c r="B30" t="b">
-        <v>0</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -855,8 +913,10 @@
       <c r="A31" t="n">
         <v>15</v>
       </c>
-      <c r="B31" t="b">
-        <v>1</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -869,8 +929,10 @@
       <c r="A32" t="n">
         <v>16</v>
       </c>
-      <c r="B32" t="b">
-        <v>0</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -883,8 +945,10 @@
       <c r="A33" t="n">
         <v>16</v>
       </c>
-      <c r="B33" t="b">
-        <v>1</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -897,8 +961,10 @@
       <c r="A34" t="n">
         <v>17</v>
       </c>
-      <c r="B34" t="b">
-        <v>0</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -911,8 +977,10 @@
       <c r="A35" t="n">
         <v>17</v>
       </c>
-      <c r="B35" t="b">
-        <v>1</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -925,8 +993,10 @@
       <c r="A36" t="n">
         <v>18</v>
       </c>
-      <c r="B36" t="b">
-        <v>0</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -939,8 +1009,10 @@
       <c r="A37" t="n">
         <v>18</v>
       </c>
-      <c r="B37" t="b">
-        <v>1</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -953,8 +1025,10 @@
       <c r="A38" t="n">
         <v>19</v>
       </c>
-      <c r="B38" t="b">
-        <v>0</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -967,8 +1041,10 @@
       <c r="A39" t="n">
         <v>19</v>
       </c>
-      <c r="B39" t="b">
-        <v>1</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -981,8 +1057,10 @@
       <c r="A40" t="n">
         <v>20</v>
       </c>
-      <c r="B40" t="b">
-        <v>0</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -995,8 +1073,10 @@
       <c r="A41" t="n">
         <v>20</v>
       </c>
-      <c r="B41" t="b">
-        <v>1</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1009,8 +1089,10 @@
       <c r="A42" t="n">
         <v>21</v>
       </c>
-      <c r="B42" t="b">
-        <v>0</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1023,8 +1105,10 @@
       <c r="A43" t="n">
         <v>21</v>
       </c>
-      <c r="B43" t="b">
-        <v>1</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1350,8 +1434,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G2" t="b">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -1416,8 +1502,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1478,8 +1566,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G4" t="b">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -1544,8 +1634,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G5" t="b">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -1610,8 +1702,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G6" t="b">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -1676,8 +1770,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G7" t="b">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -1742,8 +1838,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G8" t="b">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -1808,8 +1906,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G9" t="b">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -1870,8 +1970,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G10" t="b">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -1924,8 +2026,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G11" t="b">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1978,8 +2082,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G12" t="b">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H12" t="n">
         <v>2</v>
@@ -2032,8 +2138,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G13" t="b">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -2086,8 +2194,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G14" t="b">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -2140,8 +2250,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G15" t="b">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H15" t="n">
         <v>2</v>
@@ -2194,8 +2306,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G16" t="b">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -2248,8 +2362,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G17" t="b">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H17" t="n">
         <v>2</v>
@@ -2302,8 +2418,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G18" t="b">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H18" t="n">
         <v>2</v>
@@ -2356,8 +2474,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G19" t="b">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H19" t="n">
         <v>2</v>
@@ -2410,8 +2530,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G20" t="b">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H20" t="n">
         <v>3</v>
@@ -2468,8 +2590,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G21" t="b">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H21" t="n">
         <v>3</v>
@@ -2526,8 +2650,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G22" t="b">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -2584,8 +2710,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G23" t="b">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H23" t="n">
         <v>3</v>
@@ -2642,8 +2770,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G24" t="b">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H24" t="n">
         <v>3</v>
@@ -2700,8 +2830,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G25" t="b">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -2758,8 +2890,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G26" t="b">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H26" t="n">
         <v>3</v>
@@ -2816,8 +2950,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G27" t="b">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H27" t="n">
         <v>3</v>
@@ -2874,8 +3010,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G28" t="b">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H28" t="n">
         <v>3</v>
@@ -2932,8 +3070,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G29" t="b">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H29" t="n">
         <v>3</v>
@@ -2990,8 +3130,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G30" t="b">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H30" t="n">
         <v>3</v>
@@ -3048,8 +3190,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G31" t="b">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H31" t="n">
         <v>3</v>
@@ -3102,8 +3246,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G32" t="b">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H32" t="n">
         <v>3</v>
@@ -3156,8 +3302,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G33" t="b">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H33" t="n">
         <v>3</v>
@@ -3210,8 +3358,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G34" t="b">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H34" t="n">
         <v>3</v>
@@ -3264,8 +3414,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G35" t="b">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -3318,8 +3470,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G36" t="b">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H36" t="n">
         <v>3</v>
@@ -3372,8 +3526,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G37" t="b">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H37" t="n">
         <v>3</v>
@@ -3426,8 +3582,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G38" t="b">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H38" t="n">
         <v>3</v>
@@ -3484,8 +3642,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G39" t="b">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H39" t="n">
         <v>4</v>
@@ -3542,8 +3702,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G40" t="b">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -3604,8 +3766,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G41" t="b">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H41" t="n">
         <v>4</v>
@@ -3662,8 +3826,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G42" t="b">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H42" t="n">
         <v>4</v>
@@ -3720,8 +3886,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G43" t="b">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H43" t="n">
         <v>4</v>
@@ -3778,8 +3946,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G44" t="b">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H44" t="n">
         <v>4</v>
@@ -3832,8 +4002,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G45" t="b">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -3886,8 +4058,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G46" t="b">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H46" t="n">
         <v>4</v>
@@ -3944,8 +4118,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G47" t="b">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H47" t="n">
         <v>5</v>
@@ -4006,8 +4182,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G48" t="b">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H48" t="n">
         <v>5</v>
@@ -4068,8 +4246,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G49" t="b">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H49" t="n">
         <v>5</v>
@@ -4126,8 +4306,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G50" t="b">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H50" t="n">
         <v>5</v>
@@ -4184,8 +4366,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G51" t="b">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H51" t="n">
         <v>5</v>
@@ -4242,8 +4426,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G52" t="b">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H52" t="n">
         <v>5</v>
@@ -4300,8 +4486,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G53" t="b">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H53" t="n">
         <v>5</v>
@@ -4358,8 +4546,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G54" t="b">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H54" t="n">
         <v>5</v>
@@ -4416,8 +4606,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G55" t="b">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H55" t="n">
         <v>5</v>
@@ -4474,8 +4666,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G56" t="b">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H56" t="n">
         <v>5</v>
@@ -4532,8 +4726,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G57" t="b">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H57" t="n">
         <v>6</v>
@@ -4594,8 +4790,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G58" t="b">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H58" t="n">
         <v>6</v>
@@ -4652,8 +4850,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G59" t="b">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H59" t="n">
         <v>6</v>
@@ -4714,8 +4914,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G60" t="b">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H60" t="n">
         <v>6</v>
@@ -4776,8 +4978,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G61" t="b">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H61" t="n">
         <v>6</v>
@@ -4834,8 +5038,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G62" t="b">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H62" t="n">
         <v>6</v>
@@ -4896,8 +5102,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G63" t="b">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H63" t="n">
         <v>6</v>
@@ -4954,8 +5162,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G64" t="b">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H64" t="n">
         <v>6</v>
@@ -5016,8 +5226,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G65" t="b">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H65" t="n">
         <v>6</v>
@@ -5078,8 +5290,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G66" t="b">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H66" t="n">
         <v>6</v>
@@ -5136,8 +5350,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G67" t="b">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H67" t="n">
         <v>6</v>
@@ -5198,8 +5414,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G68" t="b">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H68" t="n">
         <v>6</v>
@@ -5256,8 +5474,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G69" t="b">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H69" t="n">
         <v>6</v>
@@ -5310,8 +5530,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G70" t="b">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H70" t="n">
         <v>6</v>
@@ -5364,8 +5586,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G71" t="b">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H71" t="n">
         <v>6</v>
@@ -5418,8 +5642,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G72" t="b">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H72" t="n">
         <v>6</v>
@@ -5472,8 +5698,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G73" t="b">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H73" t="n">
         <v>6</v>
@@ -5526,8 +5754,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G74" t="b">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H74" t="n">
         <v>16</v>
@@ -5580,8 +5810,10 @@
           <t>女</t>
         </is>
       </c>
-      <c r="G75" t="b">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H75" t="n">
         <v>16</v>
@@ -5634,8 +5866,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G76" t="b">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H76" t="n">
         <v>17</v>
@@ -5696,8 +5930,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G77" t="b">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H77" t="n">
         <v>17</v>
@@ -5758,8 +5994,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G78" t="b">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H78" t="n">
         <v>17</v>
@@ -5820,8 +6058,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G79" t="b">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H79" t="n">
         <v>18</v>
@@ -5878,8 +6118,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G80" t="b">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H80" t="n">
         <v>18</v>
@@ -5936,8 +6178,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G81" t="b">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H81" t="n">
         <v>18</v>
@@ -5994,8 +6238,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G82" t="b">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H82" t="n">
         <v>19</v>
@@ -6052,8 +6298,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G83" t="b">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H83" t="n">
         <v>19</v>
@@ -6110,8 +6358,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G84" t="b">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H84" t="n">
         <v>19</v>
@@ -6168,8 +6418,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G85" t="b">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H85" t="n">
         <v>19</v>
@@ -6226,8 +6478,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G86" t="b">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H86" t="n">
         <v>19</v>
@@ -6284,8 +6538,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G87" t="b">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H87" t="n">
         <v>19</v>
@@ -6342,8 +6598,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G88" t="b">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H88" t="n">
         <v>19</v>
@@ -6400,8 +6658,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G89" t="b">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H89" t="n">
         <v>19</v>
@@ -6458,8 +6718,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G90" t="b">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H90" t="n">
         <v>19</v>
@@ -6516,8 +6778,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G91" t="b">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H91" t="n">
         <v>20</v>
@@ -6574,8 +6838,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G92" t="b">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H92" t="n">
         <v>20</v>
@@ -6632,8 +6898,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G93" t="b">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H93" t="n">
         <v>20</v>
@@ -6690,8 +6958,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G94" t="b">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H94" t="n">
         <v>20</v>
@@ -6748,8 +7018,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G95" t="b">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H95" t="n">
         <v>20</v>
@@ -6806,8 +7078,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G96" t="b">
-        <v>0</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H96" t="n">
         <v>20</v>
@@ -6864,8 +7138,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G97" t="b">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H97" t="n">
         <v>20</v>
@@ -6922,8 +7198,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G98" t="b">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H98" t="n">
         <v>20</v>
@@ -6980,8 +7258,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G99" t="b">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H99" t="n">
         <v>20</v>
@@ -7042,8 +7322,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G100" t="b">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H100" t="n">
         <v>20</v>
@@ -7104,8 +7386,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G101" t="b">
-        <v>0</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H101" t="n">
         <v>20</v>
@@ -7162,8 +7446,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G102" t="b">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H102" t="n">
         <v>20</v>
@@ -7220,8 +7506,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G103" t="b">
-        <v>0</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H103" t="n">
         <v>20</v>
@@ -7278,8 +7566,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G104" t="b">
-        <v>0</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H104" t="n">
         <v>20</v>
@@ -7336,8 +7626,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G105" t="b">
-        <v>0</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H105" t="n">
         <v>20</v>
@@ -7394,8 +7686,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G106" t="b">
-        <v>0</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H106" t="n">
         <v>20</v>
@@ -7452,8 +7746,10 @@
           <t>男</t>
         </is>
       </c>
-      <c r="G107" t="b">
-        <v>0</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="H107" t="n">
         <v>20</v>
